--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>3.41</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.31</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1710,52 +1710,52 @@
         <v>4.07</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.41</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>2.97</v>
+        <v>2.79</v>
       </c>
       <c r="N5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.14</v>
       </c>
-      <c r="O5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.4</v>
-      </c>
       <c r="T5" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.1</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,62 +1185,62 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.85</v>
+        <v>3.41</v>
       </c>
       <c r="M6" t="n">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="N6" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="O6" t="n">
-        <v>4.12</v>
+        <v>4.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.44</v>
+        <v>3.02</v>
       </c>
       <c r="R6" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.66</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>5.81</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,58 +672,58 @@
         <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>4.01</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.92</v>
+        <v>5.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.77</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="V3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB3" t="n">
         <v>1.1</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AC3" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
         <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
         <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="Z5" t="n">
         <v>1.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,37 +1314,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.55</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>6.31</v>
+        <v>7.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="R7" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U7" t="n">
         <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -1353,22 +1353,22 @@
         <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.29</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1581,25 +1581,25 @@
         <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.81</v>
+        <v>5.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
         <v>1.06</v>
@@ -1611,22 +1611,22 @@
         <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>4.95</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>2.6</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>
@@ -1781,135 +1781,6 @@
       </c>
       <c r="AK10" s="3" t="n">
         <v>45903.58333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK11" s="3" t="n">
-        <v>45903.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.92</v>
       </c>
       <c r="O2" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.16</v>
+        <v>4.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -693,7 +693,7 @@
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
@@ -702,28 +702,28 @@
         <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.52</v>
+        <v>3.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -837,10 +837,10 @@
         <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -852,7 +852,7 @@
         <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.65</v>
+        <v>6.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>7.28</v>
+        <v>6.46</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="R7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.53</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.39</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.66</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.41</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,19 +1701,19 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
         <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
         <v>5.18</v>
@@ -1734,13 +1734,13 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="Z10" t="n">
         <v>1.46</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
         <v>1.86</v>
@@ -1781,6 +1781,135 @@
       </c>
       <c r="AK10" s="3" t="n">
         <v>45903.58333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45903.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>2.79</v>
+        <v>3.01</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1781,135 +1781,6 @@
       </c>
       <c r="AK10" s="3" t="n">
         <v>45903.58333333334</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>45903</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Hartford Athletic</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Indy Eleven</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AK11" s="3" t="n">
-        <v>45903.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.5</v>
@@ -708,10 +708,10 @@
         <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -837,10 +837,10 @@
         <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.23</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
         <v>4.1</v>
@@ -960,10 +960,10 @@
         <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
         <v>2.5</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
         <v>4.05</v>
@@ -1089,10 +1089,10 @@
         <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
         <v>2.93</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>6.46</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.66</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>2.35</v>
@@ -1476,10 +1476,10 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>2.44</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>2.6</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.36</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,49 +669,49 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X2" t="n">
         <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
@@ -720,10 +720,10 @@
         <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -816,10 +816,10 @@
         <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="T3" t="n">
         <v>3.66</v>
@@ -837,10 +837,10 @@
         <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>2.17</v>
       </c>
       <c r="O6" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.93</v>
+        <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O7" t="n">
-        <v>6.46</v>
+        <v>6.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
         <v>3.58</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.71</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,16 +1701,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="P10" t="n">
         <v>1.93</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="Y10" t="n">
         <v>2.36</v>
@@ -1755,7 +1755,7 @@
         <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.72</v>
@@ -708,10 +708,10 @@
         <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -837,10 +837,10 @@
         <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>4.05</v>
@@ -960,10 +960,10 @@
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
         <v>2.93</v>
@@ -1188,10 +1188,10 @@
         <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
         <v>4.1</v>
@@ -1218,10 +1218,10 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
         <v>2.5</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>6.24</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
         <v>2.41</v>
@@ -1476,10 +1476,10 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>2.44</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>2.58</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.36</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
         <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -693,7 +693,7 @@
         <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
         <v>1.32</v>
@@ -705,19 +705,19 @@
         <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
         <v>1.88</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.68</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -816,10 +816,10 @@
         <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="T3" t="n">
         <v>3.66</v>
@@ -834,13 +834,13 @@
         <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>3.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.26</v>
       </c>
       <c r="O6" t="n">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="P6" t="n">
         <v>1.9</v>
@@ -1206,7 +1206,7 @@
         <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="T6" t="n">
         <v>3.48</v>
@@ -1218,16 +1218,16 @@
         <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>2.61</v>
       </c>
       <c r="Y6" t="n">
         <v>2.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AA6" t="n">
         <v>4.81</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O7" t="n">
         <v>6.24</v>
@@ -1335,7 +1335,7 @@
         <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="T7" t="n">
         <v>3.58</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>11.7</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.72</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,16 +1701,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
         <v>1.93</v>
@@ -1734,13 +1734,13 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="Z10" t="n">
         <v>1.46</v>
@@ -1755,7 +1755,7 @@
         <v>2.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11.7</v>
+        <v>1.75</v>
       </c>
       <c r="M8" t="n">
-        <v>6.75</v>
+        <v>3.25</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>11.7</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>6.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.72</v>
       </c>
       <c r="P2" t="n">
-        <v>2.11</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
         <v>4.32</v>
@@ -696,7 +696,7 @@
         <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
         <v>1.03</v>
@@ -705,19 +705,19 @@
         <v>1.36</v>
       </c>
       <c r="X2" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
         <v>1.88</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>3.72</v>
@@ -816,7 +816,7 @@
         <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
         <v>2.29</v>
@@ -834,13 +834,13 @@
         <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -849,10 +849,10 @@
         <v>1.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.23</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.26</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.5</v>
+        <v>2.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.81</v>
+        <v>6.41</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M5" t="n">
         <v>2.85</v>
       </c>
-      <c r="M5" t="n">
-        <v>2.79</v>
-      </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>6.24</v>
@@ -1347,13 +1347,13 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="Z7" t="n">
         <v>1.43</v>
@@ -1362,7 +1362,7 @@
         <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC7" t="n">
         <v>2.36</v>
@@ -1443,19 +1443,19 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
         <v>6.24</v>
@@ -1476,10 +1476,10 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
         <v>2.44</v>
@@ -1497,7 +1497,7 @@
         <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.22</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.18</v>
+        <v>5.03</v>
       </c>
       <c r="R10" t="n">
         <v>1.51</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>11.7</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1781,6 +1781,135 @@
       </c>
       <c r="AK10" s="3" t="n">
         <v>45903.58333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45903.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -678,7 +678,7 @@
         <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="P2" t="n">
         <v>2.03</v>
@@ -687,10 +687,10 @@
         <v>4.32</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="T2" t="n">
         <v>3.04</v>
@@ -702,7 +702,7 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
         <v>2.84</v>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
         <v>1.73</v>
@@ -807,16 +807,16 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="P3" t="n">
         <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="S3" t="n">
         <v>2.29</v>
@@ -849,10 +849,10 @@
         <v>1.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.37</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="S4" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.41</v>
+        <v>4.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,62 +1056,62 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4.12</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA5" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.72</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>6.24</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
         <v>1.93</v>
@@ -1332,10 +1332,10 @@
         <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
         <v>3.58</v>
@@ -1353,16 +1353,16 @@
         <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AA7" t="n">
         <v>4.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
         <v>2.36</v>
@@ -1587,7 +1587,7 @@
         <v>1.93</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.24</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
         <v>1.57</v>
@@ -1617,7 +1617,7 @@
         <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="AB9" t="n">
         <v>1.12</v>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
         <v>2.06</v>
@@ -1710,13 +1710,13 @@
         <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.03</v>
+        <v>5.18</v>
       </c>
       <c r="R10" t="n">
         <v>1.51</v>
@@ -1731,7 +1731,7 @@
         <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
         <v>1.5</v>
@@ -1746,7 +1746,7 @@
         <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>4.43</v>
       </c>
       <c r="AB10" t="n">
         <v>1.12</v>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="M11" t="n">
         <v>3.45</v>
       </c>
       <c r="N11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.3</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.9</v>
+        <v>4.68</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -1869,22 +1869,22 @@
         <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.8</v>
+        <v>3.21</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
         <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.51</v>
       </c>
       <c r="O2" t="n">
         <v>2.7</v>
@@ -684,7 +684,7 @@
         <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
@@ -708,10 +708,10 @@
         <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O3" t="n">
         <v>3.7</v>
@@ -831,16 +831,16 @@
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>4.24</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.52</v>
+        <v>3.07</v>
       </c>
       <c r="R6" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="S6" t="n">
-        <v>2.13</v>
+        <v>2.39</v>
       </c>
       <c r="T6" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.93</v>
+        <v>2.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.2</v>
+        <v>4.81</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,16 +1314,16 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>6.24</v>
       </c>
       <c r="P7" t="n">
         <v>1.93</v>
@@ -1335,7 +1335,7 @@
         <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="T7" t="n">
         <v>3.58</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
         <v>2.38</v>
@@ -1590,7 +1590,7 @@
         <v>6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
         <v>2.31</v>
@@ -1605,10 +1605,10 @@
         <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="Y9" t="n">
         <v>2.44</v>
@@ -1626,7 +1626,7 @@
         <v>2.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
         <v>4.1</v>
@@ -1731,13 +1731,13 @@
         <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
         <v>1.86</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.21</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.7</v>
@@ -708,10 +708,10 @@
         <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>3.6</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.62</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>3.7</v>
@@ -831,16 +831,16 @@
         <v>1.06</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.61</v>
+        <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
         <v>3.85</v>
@@ -960,10 +960,10 @@
         <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
         <v>2.93</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>6.24</v>
@@ -1347,10 +1347,10 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
         <v>2.47</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>4.72</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>1.16</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
         <v>4.1</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>
@@ -1842,10 +1842,10 @@
         <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.68</v>
+        <v>4.79</v>
       </c>
       <c r="R11" t="n">
         <v>1.36</v>
@@ -1875,7 +1875,7 @@
         <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AB11" t="n">
         <v>1.42</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>2.13</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="R2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.43</v>
       </c>
-      <c r="S2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.84</v>
+        <v>2.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.79</v>
       </c>
       <c r="O3" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="P3" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>3.66</v>
@@ -828,19 +828,19 @@
         <v>1.22</v>
       </c>
       <c r="V3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AA3" t="n">
         <v>5.15</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,62 +1056,62 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O5" t="n">
-        <v>4.24</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.07</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.67</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="Z5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA5" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AE5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="O7" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
         <v>2.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S7" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="T7" t="n">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AB7" t="n">
         <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="O8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.72</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8</v>
+        <v>3.24</v>
       </c>
       <c r="N9" t="n">
-        <v>1.16</v>
+        <v>4.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>4.82</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,22 +1701,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.22</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P10" t="n">
         <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.18</v>
+        <v>5.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.51</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>
@@ -1746,10 +1746,10 @@
         <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
         <v>2.16</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="M11" t="n">
         <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>3.13</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.79</v>
+        <v>4.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1869,13 +1869,13 @@
         <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="AB11" t="n">
         <v>1.42</v>
@@ -1884,7 +1884,7 @@
         <v>1.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI11" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
         <v>2.9</v>
@@ -690,13 +690,13 @@
         <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
         <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
@@ -708,10 +708,10 @@
         <v>2.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>4.45</v>
@@ -720,10 +720,10 @@
         <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.79</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="U3" t="n">
         <v>1.22</v>
@@ -831,28 +831,28 @@
         <v>1.05</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="X3" t="n">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.66</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
         <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
         <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
         <v>6.23</v>
@@ -1329,7 +1329,7 @@
         <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
@@ -1347,10 +1347,10 @@
         <v>1.07</v>
       </c>
       <c r="W7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
         <v>2.53</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
         <v>2.44</v>
@@ -1587,7 +1587,7 @@
         <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.05</v>
+        <v>5.91</v>
       </c>
       <c r="R9" t="n">
         <v>1.52</v>
@@ -1605,10 +1605,10 @@
         <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>2.5</v>
@@ -1623,10 +1623,10 @@
         <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>2.62</v>
@@ -1722,7 +1722,7 @@
         <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
         <v>3.56</v>
@@ -1734,10 +1734,10 @@
         <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
         <v>2.39</v>
@@ -1749,7 +1749,7 @@
         <v>4.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AC10" t="n">
         <v>2.16</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
         <v>1.85</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>4.29</v>
+        <v>3.84</v>
       </c>
       <c r="P4" t="n">
         <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.66</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.84</v>
+        <v>4.29</v>
       </c>
       <c r="P5" t="n">
         <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>5.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>4.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="O9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.91</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="M11" t="n">
         <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>3.13</v>
@@ -1851,13 +1851,13 @@
         <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="T11" t="n">
         <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
@@ -1869,10 +1869,10 @@
         <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
         <v>3.04</v>
@@ -1881,7 +1881,7 @@
         <v>1.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AD11" t="n">
         <v>1.95</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -690,13 +690,13 @@
         <v>1.52</v>
       </c>
       <c r="S2" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
         <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
         <v>1.05</v>
@@ -717,10 +717,10 @@
         <v>4.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD2" t="n">
         <v>1.69</v>
@@ -739,7 +739,7 @@
         <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
         <v>5.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AC3" t="n">
         <v>2.12</v>
@@ -868,7 +868,7 @@
         <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.84</v>
+        <v>4.29</v>
       </c>
       <c r="P4" t="n">
         <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="Z4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.66</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1458,7 +1458,7 @@
         <v>1.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.91</v>
+        <v>6.29</v>
       </c>
       <c r="R8" t="n">
         <v>1.52</v>
@@ -1722,7 +1722,7 @@
         <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
         <v>3.56</v>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
         <v>1.85</v>
@@ -1839,34 +1839,34 @@
         <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>3.13</v>
+        <v>2.31</v>
       </c>
       <c r="P11" t="n">
         <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
         <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="Y11" t="n">
         <v>1.85</v>
@@ -1878,10 +1878,10 @@
         <v>3.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AD11" t="n">
         <v>1.95</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -687,13 +687,13 @@
         <v>4.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
         <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="U2" t="n">
         <v>1.27</v>
@@ -717,13 +717,13 @@
         <v>4.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -807,19 +807,19 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.64</v>
+        <v>3.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
         <v>3.64</v>
@@ -843,7 +843,7 @@
         <v>1.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="AB3" t="n">
         <v>1.1</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>4.29</v>
+        <v>3.87</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.19</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="T4" t="n">
-        <v>3.66</v>
+        <v>4.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.66</v>
+        <v>6</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>3.84</v>
+        <v>4.34</v>
       </c>
       <c r="P5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>3.19</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>3.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>5.74</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1329,7 +1329,7 @@
         <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R7" t="n">
         <v>1.58</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AH7" t="n">
         <v>1.14</v>
@@ -1485,13 +1485,13 @@
         <v>2.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
         <v>4.82</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
         <v>2.36</v>
@@ -1710,19 +1710,19 @@
         <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.12</v>
+        <v>5.23</v>
       </c>
       <c r="R10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S10" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
         <v>3.56</v>
@@ -1746,13 +1746,13 @@
         <v>1.46</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD10" t="n">
         <v>1.63</v>
@@ -1771,7 +1771,7 @@
         <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.94</v>
+        <v>4.89</v>
       </c>
       <c r="R11" t="n">
         <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
         <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="Y11" t="n">
         <v>1.85</v>
@@ -1875,16 +1875,16 @@
         <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
         <v>1.95</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.29</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.16</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>2.9</v>
@@ -684,7 +684,7 @@
         <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.34</v>
+        <v>3.74</v>
       </c>
       <c r="R2" t="n">
         <v>1.53</v>
@@ -693,7 +693,7 @@
         <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.27</v>
@@ -708,10 +708,10 @@
         <v>2.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA2" t="n">
         <v>4.45</v>
@@ -720,10 +720,10 @@
         <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="P3" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.86</v>
+        <v>3.29</v>
       </c>
       <c r="R3" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.64</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>2.66</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1056,34 +1056,34 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>4.34</v>
+        <v>3.95</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.19</v>
+        <v>3.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="T5" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
         <v>1.06</v>
@@ -1092,25 +1092,25 @@
         <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.44</v>
+        <v>2.71</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.74</v>
+        <v>5.35</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
         <v>1.31</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="O7" t="n">
-        <v>6.23</v>
+        <v>6.13</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="R7" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S7" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="T7" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.95</v>
+        <v>4.8</v>
       </c>
       <c r="AB7" t="n">
         <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>2.11</v>
+        <v>1.24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1572,46 +1572,46 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>3.32</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="O9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.29</v>
+        <v>6.23</v>
       </c>
       <c r="R9" t="n">
         <v>1.52</v>
       </c>
       <c r="S9" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="Z9" t="n">
         <v>1.5</v>
@@ -1623,10 +1623,10 @@
         <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.14</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,49 +1701,49 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.23</v>
+        <v>5.18</v>
       </c>
       <c r="R10" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.5</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.46</v>
       </c>
       <c r="AA10" t="n">
         <v>4.45</v>
@@ -1752,10 +1752,10 @@
         <v>1.19</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.02</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="P11" t="n">
-        <v>2.33</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.89</v>
+        <v>4.99</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S11" t="n">
         <v>2.98</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X11" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AI11" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -669,31 +669,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
         <v>1.93</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.74</v>
+        <v>4.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S2" t="n">
         <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>3.29</v>
       </c>
       <c r="U2" t="n">
         <v>1.27</v>
@@ -708,10 +708,10 @@
         <v>2.47</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="n">
         <v>4.45</v>
@@ -720,10 +720,10 @@
         <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
         <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.3</v>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.84</v>
-      </c>
       <c r="O3" t="n">
-        <v>3.14</v>
+        <v>2.99</v>
       </c>
       <c r="P3" t="n">
         <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.29</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
         <v>3.48</v>
@@ -831,22 +831,22 @@
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z3" t="n">
         <v>1.48</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.47</v>
       </c>
       <c r="AA3" t="n">
         <v>4.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
         <v>2.03</v>
@@ -868,7 +868,7 @@
         <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="M5" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.36</v>
+        <v>2.9</v>
       </c>
       <c r="O5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="P5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="S5" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="T5" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="U5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
         <v>2.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.35</v>
+        <v>5.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.19</v>
+        <v>2.29</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,25 +1314,25 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O7" t="n">
-        <v>6.13</v>
+        <v>5.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.31</v>
+        <v>2.49</v>
       </c>
       <c r="R7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S7" t="n">
         <v>2.31</v>
@@ -1347,28 +1347,28 @@
         <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.8</v>
+        <v>5.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.76</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>3.32</v>
+        <v>6.8</v>
       </c>
       <c r="N9" t="n">
-        <v>4.25</v>
+        <v>1.16</v>
       </c>
       <c r="O9" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.82</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="M10" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="T10" t="n">
         <v>3.4</v>
@@ -1734,28 +1734,28 @@
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X10" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AA10" t="n">
         <v>4.45</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>1.16</v>
       </c>
       <c r="O8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -687,13 +687,13 @@
         <v>4.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="T2" t="n">
-        <v>3.29</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
         <v>1.27</v>
@@ -714,7 +714,7 @@
         <v>1.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB2" t="n">
         <v>1.14</v>
@@ -807,19 +807,19 @@
         <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="P3" t="n">
         <v>1.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.04</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
         <v>3.48</v>
@@ -849,10 +849,10 @@
         <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="N4" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>3.9</v>
+        <v>4.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="U4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.82</v>
+        <v>2.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.9</v>
+        <v>5.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>4.39</v>
+        <v>3.9</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="S6" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>3.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.37</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.19</v>
+        <v>2.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1356,16 +1356,16 @@
         <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.46</v>
+        <v>4.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.42</v>
+        <v>2.29</v>
       </c>
       <c r="AD7" t="n">
         <v>1.56</v>
@@ -1381,7 +1381,7 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH7" t="n">
         <v>1.17</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>14</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.88</v>
+        <v>4.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.9</v>
+        <v>15</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>4.5</v>
+        <v>1.08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6.33</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z9" t="n">
         <v>2.54</v>
       </c>
-      <c r="Z9" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AA9" t="n">
-        <v>4.6</v>
+        <v>1.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,19 +1710,19 @@
         <v>4.1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="P10" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.22</v>
+        <v>5.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="T10" t="n">
         <v>3.4</v>
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="P11" t="n">
         <v>2.16</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.99</v>
+        <v>4.9</v>
       </c>
       <c r="R11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>1.23</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK11"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,27 +628,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yenisey</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.66</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5</v>
+        <v>3.74</v>
       </c>
       <c r="O2" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>1.61</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45903.375</v>
+        <v>45903.25</v>
       </c>
     </row>
     <row r="3">
@@ -757,27 +757,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.25</v>
+        <v>2.17</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.45</v>
+        <v>1.75</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45903.47916666666</v>
+        <v>45903.27083333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Yenisey</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M4" t="n">
         <v>3.15</v>
       </c>
-      <c r="M4" t="n">
-        <v>2.85</v>
-      </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q4" t="n">
         <v>4.34</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3.02</v>
-      </c>
       <c r="R4" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="T4" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.5</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AA4" t="n">
-        <v>5.45</v>
+        <v>4.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45903.5</v>
+        <v>45903.375</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45903.5</v>
+        <v>45903.47916666666</v>
       </c>
     </row>
     <row r="6">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,34 +1314,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>5.5</v>
+        <v>4.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.49</v>
+        <v>3.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S7" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.06</v>
@@ -1353,22 +1353,22 @@
         <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.85</v>
+        <v>5.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45903.52083333334</v>
+        <v>45903.5</v>
       </c>
     </row>
     <row r="8">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45903.54166666666</v>
+        <v>45903.5</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M9" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.43</v>
+        <v>2.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.54</v>
+        <v>1.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.88</v>
+        <v>4.85</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45903.54166666666</v>
+        <v>45903.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="M10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.32</v>
+        <v>6.23</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="T10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.11</v>
+        <v>2.29</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45903.58333333334</v>
+        <v>45903.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,126 +1789,384 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Norway Toppserien</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Hønefoss Women</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vålerenga Women</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45903.54166666666</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKA Khabarovsk</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.32</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45903.58333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>USA USL Championship</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Hartford Athletic</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Indy Eleven</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>2.02</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M13" t="n">
         <v>3.45</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N13" t="n">
         <v>3.35</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O13" t="n">
         <v>2.22</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P13" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q13" t="n">
         <v>4.9</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R13" t="n">
         <v>1.33</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S13" t="n">
         <v>3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>2.4</v>
       </c>
-      <c r="U11" t="n">
+      <c r="U13" t="n">
         <v>1.48</v>
       </c>
-      <c r="V11" t="n">
+      <c r="V13" t="n">
         <v>1.01</v>
       </c>
-      <c r="W11" t="n">
+      <c r="W13" t="n">
         <v>1.21</v>
       </c>
-      <c r="X11" t="n">
+      <c r="X13" t="n">
         <v>3.9</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y13" t="n">
         <v>1.85</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z13" t="n">
         <v>1.85</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AA13" t="n">
         <v>3.05</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AB13" t="n">
         <v>1.42</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC13" t="n">
         <v>1.78</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD13" t="n">
         <v>2.2</v>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
         <v>1.23</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AH13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AI13" t="n">
         <v>2.2</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ13" t="n">
         <v>1.8</v>
       </c>
-      <c r="AK11" s="3" t="n">
+      <c r="AK13" s="3" t="n">
         <v>45903.85416666666</v>
       </c>
     </row>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -665,17 +665,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.66</v>
+        <v>3.85</v>
       </c>
       <c r="N2" t="n">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -794,17 +794,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.17</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N3" t="n">
-        <v>2.94</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -923,65 +923,65 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="M4" t="n">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="O4" t="n">
-        <v>2.88</v>
+        <v>3.16</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.34</v>
+        <v>3.98</v>
       </c>
       <c r="R4" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S4" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.43</v>
       </c>
-      <c r="X4" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA4" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1065,28 +1065,28 @@
         <v>2.3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.89</v>
+        <v>3.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="T5" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
         <v>1.55</v>
@@ -1101,16 +1101,16 @@
         <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1194,28 +1194,28 @@
         <v>2.9</v>
       </c>
       <c r="O6" t="n">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="P6" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
         <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="T6" t="n">
         <v>3.98</v>
       </c>
       <c r="U6" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
         <v>1.52</v>
@@ -1224,22 +1224,22 @@
         <v>2.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AH6" t="n">
         <v>1.4</v>
@@ -1323,28 +1323,28 @@
         <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>4.34</v>
+        <v>5.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.02</v>
+        <v>2.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="S7" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="T7" t="n">
-        <v>3.85</v>
+        <v>4.55</v>
       </c>
       <c r="U7" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.5</v>
@@ -1359,32 +1359,32 @@
         <v>1.53</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.45</v>
+        <v>7.1</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.27</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1581,28 +1581,28 @@
         <v>1.75</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="T9" t="n">
-        <v>3.58</v>
+        <v>3.66</v>
       </c>
       <c r="U9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
         <v>1.5</v>
@@ -1611,22 +1611,22 @@
         <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="AB9" t="n">
         <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1710,28 +1710,28 @@
         <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.42</v>
+        <v>2.13</v>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.23</v>
+        <v>7.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.31</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="V10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
@@ -1740,22 +1740,22 @@
         <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.54</v>
+        <v>2.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1968,28 +1968,28 @@
         <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="P12" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.32</v>
+        <v>5.15</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
         <v>1.5</v>
@@ -2004,16 +2004,16 @@
         <v>1.46</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.11</v>
+        <v>2.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
         <v>1.9</v>
@@ -2088,34 +2088,34 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3.45</v>
+        <v>3.71</v>
       </c>
       <c r="N13" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="O13" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="P13" t="n">
         <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
@@ -2127,22 +2127,22 @@
         <v>3.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="AB13" t="n">
         <v>1.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.97</v>
       </c>
       <c r="AI13" t="n">
         <v>2.2</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1039,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1297,94 +1297,94 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="O7" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="R7" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="S7" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="T7" t="n">
-        <v>4.55</v>
+        <v>3.66</v>
       </c>
       <c r="U7" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.1</v>
+        <v>5.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15', '38', '60', '75', '90+2']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,87 +1417,87 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1506,14 +1506,14 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '90+5']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1558,42 +1558,42 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="O9" t="n">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="T9" t="n">
         <v>3.66</v>
@@ -1605,28 +1605,28 @@
         <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="X9" t="n">
         <v>2.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.77</v>
+        <v>2.56</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1635,14 +1635,14 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '43', '58', '66', '82', '90+2']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.96</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R10" t="n">
         <v>1.51</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="T10" t="n">
         <v>3.34</v>
@@ -1734,28 +1734,28 @@
         <v>1.05</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.23</v>
+        <v>2.37</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.39</v>
+        <v>2.61</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
         <v>3.05</v>
@@ -1968,19 +1968,19 @@
         <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="T12" t="n">
         <v>3.56</v>
@@ -1989,31 +1989,31 @@
         <v>1.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.39</v>
+        <v>2.51</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AB12" t="n">
         <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="M13" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
         <v>2.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.7</v>
+        <v>4.35</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
         <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V13" t="n">
         <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
         <v>3.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.09</v>
+        <v>2.62</v>
       </c>
       <c r="AB13" t="n">
         <v>1.42</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
         <v>1.97</v>

--- a/jogos_2025-09-03.xlsx
+++ b/jogos_2025-09-03.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,87 +1159,87 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Baník Ostrava II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '90+5']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Baník Ostrava II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
+          <t>['64', '69', '89']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['36', '90+5']</t>
-        </is>
-      </c>
       <c r="AG8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -1839,13 +1839,13 @@
         <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG11" t="n">
@@ -1903,10 +1903,10 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45903.54166666666</v>
@@ -1942,20 +1942,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['36', '42', '46']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AG12" t="n">
